--- a/panchang-data/Rameshwaram2026.xlsx
+++ b/panchang-data/Rameshwaram2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5343">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16054,6 +16054,9 @@
   </si>
   <si>
     <t>121°05'09.32</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16543,7 +16546,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16629,7 +16632,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16715,7 +16718,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16801,7 +16804,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -16887,7 +16890,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -16973,7 +16976,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17059,7 +17062,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17145,7 +17148,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17231,7 +17234,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17317,7 +17320,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17403,7 +17406,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17489,7 +17492,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17575,7 +17578,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17661,7 +17664,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17747,7 +17750,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17833,7 +17836,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -17919,7 +17922,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18005,7 +18008,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18091,7 +18094,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18177,7 +18180,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18263,7 +18266,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18349,7 +18352,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18435,7 +18438,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18521,7 +18524,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18607,7 +18610,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18693,7 +18696,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18779,7 +18782,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -18865,7 +18868,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -18951,7 +18954,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19037,7 +19040,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19123,7 +19126,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19209,7 +19212,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19295,7 +19298,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19381,7 +19384,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19467,7 +19470,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19553,7 +19556,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19639,7 +19642,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19725,7 +19728,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19811,7 +19814,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -19897,7 +19900,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -19983,7 +19986,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20069,7 +20072,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20155,7 +20158,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20241,7 +20244,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20327,7 +20330,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20413,7 +20416,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20499,7 +20502,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20585,7 +20588,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20671,7 +20674,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20757,7 +20760,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20843,7 +20846,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -20929,7 +20932,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21015,7 +21018,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21101,7 +21104,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21187,7 +21190,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21273,7 +21276,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21359,7 +21362,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21445,7 +21448,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21531,7 +21534,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21617,7 +21620,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21703,7 +21706,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21789,7 +21792,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1008</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -21875,7 +21878,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -21961,7 +21964,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22047,7 +22050,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22133,7 +22136,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22219,7 +22222,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22305,7 +22308,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22391,7 +22394,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22477,7 +22480,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22563,7 +22566,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22649,7 +22652,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22735,7 +22738,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22821,7 +22824,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -22907,7 +22910,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -22993,7 +22996,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23079,7 +23082,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23165,7 +23168,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23251,7 +23254,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23337,7 +23340,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23423,7 +23426,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23509,7 +23512,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23595,7 +23598,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23681,7 +23684,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23767,7 +23770,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23853,7 +23856,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -23939,7 +23942,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24025,7 +24028,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24111,7 +24114,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24197,7 +24200,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24283,7 +24286,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24369,7 +24372,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1008</v>
+        <v>1440</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24455,7 +24458,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24541,7 +24544,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24627,7 +24630,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24713,7 +24716,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24799,7 +24802,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -24885,7 +24888,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -24971,7 +24974,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25057,7 +25060,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25143,7 +25146,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25229,7 +25232,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25315,7 +25318,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25401,7 +25404,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25487,7 +25490,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25573,7 +25576,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25659,7 +25662,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25745,7 +25748,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25831,7 +25834,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -25917,7 +25920,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26003,7 +26006,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26089,7 +26092,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26175,7 +26178,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26261,7 +26264,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26347,7 +26350,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26433,7 +26436,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26519,7 +26522,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26605,7 +26608,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26691,7 +26694,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26777,7 +26780,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26863,7 +26866,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1440</v>
+        <v>1851</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -26949,7 +26952,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27035,7 +27038,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27121,7 +27124,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27207,7 +27210,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27293,7 +27296,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27379,7 +27382,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27465,7 +27468,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27551,7 +27554,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27637,7 +27640,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27723,7 +27726,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27809,7 +27812,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -27895,7 +27898,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -27981,7 +27984,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28067,7 +28070,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28153,7 +28156,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1851</v>
+        <v>2282</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28239,7 +28242,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28325,7 +28328,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28411,7 +28414,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28497,7 +28500,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28583,7 +28586,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28669,7 +28672,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28755,7 +28758,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28841,7 +28844,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -28927,7 +28930,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29013,7 +29016,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29099,7 +29102,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29185,7 +29188,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29271,7 +29274,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29357,7 +29360,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29443,7 +29446,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1851</v>
+        <v>5342</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29529,7 +29532,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29615,7 +29618,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29701,7 +29704,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29787,7 +29790,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -29873,7 +29876,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -29959,7 +29962,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30045,7 +30048,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30131,7 +30134,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30217,7 +30220,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30303,7 +30306,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30389,7 +30392,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30475,7 +30478,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30561,7 +30564,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30647,7 +30650,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30733,7 +30736,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2282</v>
+        <v>5342</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
